--- a/dom_rf_data.xlsx
+++ b/dom_rf_data.xlsx
@@ -413,9 +413,138 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ID объекта</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Застройщик</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Адрес</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ID Декларации</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Путь к файлу на ПК</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Выдержка из декларации</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>00088</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Застройщик (информация внутри PDF)</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Дом из каталога (ID 00088)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>/api/ext/file/declaration_00088</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Файл не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>01778</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Застройщик (информация внутри PDF)</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Дом из каталога (ID 01778)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>/api/ext/file/declaration_01778</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Файл не скачан</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>93803</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Застройщик (информация внутри PDF)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Дом из каталога (ID 93803)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>/api/ext/file/declaration_93803</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ошибка</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Файл не скачан</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/dom_rf_data.xlsx
+++ b/dom_rf_data.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,7 +466,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>/api/ext/file/declaration_00088</t>
+          <t>Определится при скачивании</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -498,7 +498,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>/api/ext/file/declaration_01778</t>
+          <t>Определится при скачивании</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -507,38 +507,6 @@
         </is>
       </c>
       <c r="F3" t="inlineStr">
-        <is>
-          <t>Файл не скачан</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>93803</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Застройщик (информация внутри PDF)</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Дом из каталога (ID 93803)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>/api/ext/file/declaration_93803</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Ошибка</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
         <is>
           <t>Файл не скачан</t>
         </is>
